--- a/manufacturing_forms/020_product_test_revalidation_request_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/020_product_test_revalidation_request_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'subcategory_1'}</t>
+          <t>subcategory_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Subcategory 1'}</t>
+          <t>Subcategory 1</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'subcategory_2'}</t>
+          <t>subcategory_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Subcategory 2'}</t>
+          <t>Subcategory 2</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'subcategory_3'}</t>
+          <t>subcategory_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Subcategory 3'}</t>
+          <t>Subcategory 3</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'revalidated'}</t>
+          <t>revalidated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Revalidated'}</t>
+          <t>Revalidated</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Type 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Type 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Type 3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
